--- a/reports/pdf_rolling5_20260723.xlsx
+++ b/reports/pdf_rolling5_20260723.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,306억   ·   현금 53억(1.3%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 20종목  /  매도 19종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,207억   ·   현금 54억(1.3%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 20종목  /  매도 19종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>238</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>7599209100</v>
+        <v>7630006300</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-50</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-590226000</v>
+        <v>-592618000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>229</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>846456135</v>
+        <v>849886555</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-47</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1681601250</v>
+        <v>-1688416250</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>106</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1432275180</v>
+        <v>1438079740</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -772,18 +772,18 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍  (편출)</t>
+          <t>코오롱생명과학  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-45</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2011999500</v>
+        <v>-1670082750</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.00%</t>
+          <t>0.37%→0.00%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -802,7 +802,7 @@
         <v>82</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1259333040</v>
+        <v>1264436720</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -816,18 +816,18 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>코오롱생명과학  (편출)</t>
+          <t>에스앤에스텍  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-45</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1663341750</v>
+        <v>-2020153500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.00%</t>
+          <t>0.45%→0.00%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>445985820</v>
+        <v>447793260</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-856321200</v>
+        <v>-859791600</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1987719300</v>
+        <v>1995774900</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-34</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-428871240</v>
+        <v>-430609320</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>37</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>411934320</v>
+        <v>413603760</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-30</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-874975500</v>
+        <v>-878521500</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>33</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2292998400</v>
+        <v>2302291200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-29</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1791799800</v>
+        <v>-1799061400</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>3853248000</v>
+        <v>3868864000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-26</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-423166380</v>
+        <v>-424881340</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>661734150</v>
+        <v>664415950</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-21</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-3243775500</v>
+        <v>-3256921500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>875074200</v>
+        <v>878620600</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-15</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-420462000</v>
+        <v>-422166000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>765714600</v>
+        <v>768817800</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-359268000</v>
+        <v>-360724000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1155974400</v>
+        <v>1160659200</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-404867400</v>
+        <v>-390553100</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.89%</t>
+          <t>0.56%→0.47%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>397366200</v>
+        <v>398976600</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1256,23 +1256,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-388976700</v>
+        <v>-406508200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.47%</t>
+          <t>0.87%→0.89%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>416908800</v>
+        <v>418598400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-10</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-386904000</v>
+        <v>-388472000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1733172000</v>
+        <v>1740196000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-881983200</v>
+        <v>-885557600</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>773314500</v>
+        <v>776448500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-349398000</v>
+        <v>-350814000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>4</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1889118000</v>
+        <v>1896774000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-410986800</v>
+        <v>-412652400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>387298800</v>
+        <v>388868400</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>-3</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-304983000</v>
+        <v>-306219000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>710640000</v>
+        <v>713520000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,742억   ·   현금 29억(0.8%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 5종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,697억   ·   현금 29억(0.8%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 5종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1772,7 +1772,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,467억   ·   현금 88억(3.6%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 2종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,423억   ·   현금 88억(3.6%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1868,7 +1868,7 @@
         <v>150</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>3611902500</v>
+        <v>3627675000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1882,18 +1882,18 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2225880000</v>
+        <v>-1132980000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>7.48%→6.15%</t>
+          <t>4.46%→3.12%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1912,7 +1912,7 @@
         <v>122</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>2711382900</v>
+        <v>2723223000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1926,18 +1926,18 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1128054000</v>
+        <v>-2235600000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.12%</t>
+          <t>7.48%→6.15%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1961,7 +1961,7 @@
         <v>-19</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2045405100</v>
+        <v>-2054337000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
     <row r="43" ht="19" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,226억   ·   현금 48억(2.2%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,183억   ·   현금 48억(2.2%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B43" s="4" t="n"/>
@@ -2001,7 +2001,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 281억   ·   현금 -1억(-0.2%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 9종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 -1억(-0.2%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 9종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2097,11 +2097,11 @@
         <v>485</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>126429800</v>
+        <v>131221600</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.45%</t>
+          <t>0.00%→0.48%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2118,11 +2118,11 @@
         <v>-108</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-53023680</v>
+        <v>-54008640</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.81%</t>
+          <t>1.06%→0.85%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2141,11 +2141,11 @@
         <v>201</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>113500680</v>
+        <v>110903760</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>6.54%→6.90%</t>
+          <t>6.55%→6.89%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2162,11 +2162,11 @@
         <v>-73</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-78171320</v>
+        <v>-77061720</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.62%→1.33%</t>
+          <t>1.64%→1.34%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2185,11 +2185,11 @@
         <v>93</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>197550600</v>
+        <v>190836000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>5.47%→6.13%</t>
+          <t>5.41%→6.05%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2206,11 +2206,11 @@
         <v>-18</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-75376800</v>
+        <v>-65595600</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>1.61%→1.33%</t>
+          <t>1.43%→1.18%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2229,11 +2229,11 @@
         <v>45</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>70965000</v>
+        <v>72504000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>2.99%→3.22%</t>
+          <t>3.13%→3.36%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2250,11 +2250,11 @@
         <v>-10</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-67488000</v>
+        <v>-67184000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>1.26%→1.01%</t>
+          <t>1.28%→1.03%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2273,11 +2273,11 @@
         <v>26</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>33592000</v>
+        <v>35587760</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.41%</t>
+          <t>0.32%→0.44%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2294,11 +2294,11 @@
         <v>-9</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-74692800</v>
+        <v>-70452000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.00%</t>
+          <t>0.26%→0.00%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2317,11 +2317,11 @@
         <v>25</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>54625000</v>
+        <v>56145000</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.84%</t>
+          <t>2.81%→2.98%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2338,11 +2338,11 @@
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-71820000</v>
+        <v>-64904000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.46%→3.18%</t>
+          <t>3.20%→2.94%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2361,11 +2361,11 @@
         <v>18</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>49521600</v>
+        <v>49590000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>7.21%→7.33%</t>
+          <t>7.39%→7.50%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2382,11 +2382,11 @@
         <v>-5</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-54188000</v>
+        <v>-49704000</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>1.40%→1.20%</t>
+          <t>1.32%→1.12%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2405,11 +2405,11 @@
         <v>18</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>76334400</v>
+        <v>85636800</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>1.99%→2.25%</t>
+          <t>2.29%→2.58%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2419,23 +2419,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-35294400</v>
+        <v>-24958400</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.94%→2.80%</t>
+          <t>3.33%→3.20%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>93→89</t>
+          <t>145→141</t>
         </is>
       </c>
     </row>
@@ -2449,11 +2449,11 @@
         <v>6</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>46010400</v>
+        <v>44505600</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.01%→2.16%</t>
+          <t>1.99%→2.13%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2463,23 +2463,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-27147200</v>
+        <v>-33956800</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.53%→3.41%</t>
+          <t>2.90%→2.75%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>145→141</t>
+          <t>93→89</t>
         </is>
       </c>
     </row>
@@ -2498,11 +2498,11 @@
         <v>-3</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-37779600</v>
+        <v>-35682000</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.16%→3.00%</t>
+          <t>3.06%→2.90%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2514,7 +2514,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 469억   ·   현금 1억(0.3%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 2종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 456억   ·   현금 1억(0.3%)      오늘 2026-07-23  vs  5일전 2026-07-15      매수 2종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260723.xlsx
+++ b/reports/pdf_rolling5_20260723.xlsx
@@ -1168,46 +1168,46 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-360724000</v>
+        <v>-406508200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.26%</t>
+          <t>0.87%→0.89%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1160659200</v>
+        <v>398976600</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>3.98%→4.17%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,44 +1235,44 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>398976600</v>
+        <v>1160659200</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>3.98%→4.17%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-406508200</v>
+        <v>-360724000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.89%</t>
+          <t>0.35%→0.26%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
@@ -1388,23 +1388,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-350814000</v>
+        <v>-412652400</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.26%→1.04%</t>
+          <t>2.25%→2.18%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1432,46 +1432,46 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-412652400</v>
+        <v>-350814000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.25%→2.18%</t>
+          <t>1.26%→1.04%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>388868400</v>
+        <v>713520000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.24%→1.21%</t>
+          <t>2.49%→2.51%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>41→44</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1499,23 +1499,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>713520000</v>
+        <v>388868400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.51%</t>
+          <t>1.24%→1.21%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>41→44</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1882,18 +1882,18 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1132980000</v>
+        <v>-2235600000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.12%</t>
+          <t>7.48%→6.15%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1926,18 +1926,18 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-2235600000</v>
+        <v>-1132980000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>7.48%→6.15%</t>
+          <t>4.46%→3.12%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -2354,23 +2354,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>49590000</v>
+        <v>85636800</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>7.39%→7.50%</t>
+          <t>2.29%→2.58%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>730→748</t>
+          <t>131→149</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2398,44 +2398,44 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>85636800</v>
+        <v>49590000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.29%→2.58%</t>
+          <t>7.39%→7.50%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>131→149</t>
+          <t>730→748</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-24958400</v>
+        <v>-33956800</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>3.33%→3.20%</t>
+          <t>2.90%→2.75%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>145→141</t>
+          <t>93→89</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-33956800</v>
+        <v>-24958400</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.75%</t>
+          <t>3.33%→3.20%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>93→89</t>
+          <t>145→141</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260723.xlsx
+++ b/reports/pdf_rolling5_20260723.xlsx
@@ -1168,134 +1168,134 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-406508200</v>
+        <v>-390553100</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.89%</t>
+          <t>0.56%→0.47%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>142→128</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>398976600</v>
+        <v>418598400</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>0.65%→0.79%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-390553100</v>
+        <v>-360724000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.47%</t>
+          <t>0.35%→0.26%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1160659200</v>
+        <v>398976600</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>3.98%→4.17%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-360724000</v>
+        <v>-406508200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.26%</t>
+          <t>0.87%→0.89%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>142→128</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>418598400</v>
+        <v>1160659200</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.65%→0.79%</t>
+          <t>3.98%→4.17%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1455,23 +1455,23 @@
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>713520000</v>
+        <v>388868400</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.51%</t>
+          <t>1.24%→1.21%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>41→44</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1499,23 +1499,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>388868400</v>
+        <v>713520000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.24%→1.21%</t>
+          <t>2.49%→2.51%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>41→44</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1882,18 +1882,18 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2235600000</v>
+        <v>-1132980000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>7.48%→6.15%</t>
+          <t>4.46%→3.12%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1926,18 +1926,18 @@
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
         <v>-20</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1132980000</v>
+        <v>-2235600000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>4.46%→3.12%</t>
+          <t>7.48%→6.15%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -2419,23 +2419,23 @@
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-33956800</v>
+        <v>-24958400</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.90%→2.75%</t>
+          <t>3.33%→3.20%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>93→89</t>
+          <t>145→141</t>
         </is>
       </c>
     </row>
@@ -2463,23 +2463,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-24958400</v>
+        <v>-33956800</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>3.33%→3.20%</t>
+          <t>2.90%→2.75%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>145→141</t>
+          <t>93→89</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260723.xlsx
+++ b/reports/pdf_rolling5_20260723.xlsx
@@ -772,18 +772,18 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>코오롱생명과학  (편출)</t>
+          <t>에스앤에스텍  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-45</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1670082750</v>
+        <v>-2020153500</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.00%</t>
+          <t>0.45%→0.00%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -816,18 +816,18 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍  (편출)</t>
+          <t>코오롱생명과학  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-45</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2020153500</v>
+        <v>-1670082750</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.00%</t>
+          <t>0.37%→0.00%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -1168,90 +1168,90 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-390553100</v>
+        <v>-360724000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.56%→0.47%</t>
+          <t>0.35%→0.26%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>84→70</t>
+          <t>56→42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>418598400</v>
+        <v>1160659200</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.65%→0.79%</t>
+          <t>3.98%→4.17%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-14</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-360724000</v>
+        <v>-390553100</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.26%</t>
+          <t>0.56%→0.47%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>56→42</t>
+          <t>84→70</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>398976600</v>
+        <v>418598400</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>0.65%→0.79%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1160659200</v>
+        <v>398976600</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>3.98%→4.17%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1388,23 +1388,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-412652400</v>
+        <v>-350814000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.25%→2.18%</t>
+          <t>1.26%→1.04%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
@@ -1432,46 +1432,46 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-350814000</v>
+        <v>-412652400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.26%→1.04%</t>
+          <t>2.25%→2.18%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>388868400</v>
+        <v>713520000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.24%→1.21%</t>
+          <t>2.49%→2.51%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>36→39</t>
+          <t>41→44</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -1499,23 +1499,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>713520000</v>
+        <v>388868400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>2.49%→2.51%</t>
+          <t>1.24%→1.21%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>41→44</t>
+          <t>36→39</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -2354,23 +2354,23 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>85636800</v>
+        <v>49590000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>2.29%→2.58%</t>
+          <t>7.39%→7.50%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>131→149</t>
+          <t>730→748</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2398,23 +2398,23 @@
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>49590000</v>
+        <v>85636800</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>7.39%→7.50%</t>
+          <t>2.29%→2.58%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>730→748</t>
+          <t>131→149</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260723.xlsx
+++ b/reports/pdf_rolling5_20260723.xlsx
@@ -772,18 +772,18 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>에스앤에스텍  (편출)</t>
+          <t>코오롱생명과학  (편출)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>-45</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2020153500</v>
+        <v>-1670082750</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.45%→0.00%</t>
+          <t>0.37%→0.00%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -816,18 +816,18 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>코오롱생명과학  (편출)</t>
+          <t>에스앤에스텍  (편출)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
         <v>-45</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1670082750</v>
+        <v>-2020153500</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.37%→0.00%</t>
+          <t>0.45%→0.00%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1160659200</v>
+        <v>398976600</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>3.98%→4.17%</t>
+          <t>0.52%→0.62%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>168→180</t>
+          <t>66→78</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>418598400</v>
+        <v>1160659200</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.65%→0.79%</t>
+          <t>3.98%→4.17%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>82→94</t>
+          <t>168→180</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>398976600</v>
+        <v>418598400</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.52%→0.62%</t>
+          <t>0.65%→0.79%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>66→78</t>
+          <t>82→94</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1388,23 +1388,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-350814000</v>
+        <v>-412652400</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>1.26%→1.04%</t>
+          <t>2.25%→2.18%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>80→74</t>
+          <t>138→132</t>
         </is>
       </c>
     </row>
@@ -1432,23 +1432,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-412652400</v>
+        <v>-350814000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>2.25%→2.18%</t>
+          <t>1.26%→1.04%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>138→132</t>
+          <t>80→74</t>
         </is>
       </c>
     </row>
